--- a/BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx
+++ b/BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="249">
   <si>
     <t xml:space="preserve">BSI.IT.27.C7 – Network Device Admin Account Review – Sample of One Workpaper (MIA25142)</t>
   </si>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">IAMS Termination Date / Identity Inactive fields; AD 05/15/2026 row 1636; Oct10_2026Users row 1621</t>
   </si>
   <si>
-    <t xml:space="preserve">Evidence index – BSI.IT.27.C7 (E01 – E08)</t>
+    <t xml:space="preserve">Evidence index – BSI.IT.27.C7 (E01 – E09)</t>
   </si>
   <si>
     <t xml:space="preserve">Same references as the "Evidence references" table of the Word document.</t>
@@ -641,6 +641,18 @@
     <t xml:space="preserve">Evidence references</t>
   </si>
   <si>
+    <t xml:space="preserve">E09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx (this workbook)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample result, attribute testing, evidence map and index for MIA25142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary box; Section 3 (evidence column, conclusion); Evidence references E09; Exhibits A1-A5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cross-reference: BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx → this workbook</t>
   </si>
   <si>
@@ -713,10 +725,10 @@
     <t xml:space="preserve">WP Summary!B9; Sample Attribute Testing (result line)</t>
   </si>
   <si>
-    <t xml:space="preserve">E01-E08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence Index!A5:G12</t>
+    <t xml:space="preserve">E01-E09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence Index!A5:G13</t>
   </si>
   <si>
     <t xml:space="preserve">Exhibit A1</t>
@@ -2220,7 +2232,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2459,6 +2471,29 @@
       </c>
       <c r="G12" s="6" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2491,31 +2526,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2523,65 +2558,65 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2589,65 +2624,65 @@
         <v>204</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx
+++ b/BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="270">
   <si>
     <t xml:space="preserve">BSI.IT.27.C7 – Network Device Admin Account Review – Sample of One Workpaper (MIA25142)</t>
   </si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Design rating</t>
   </si>
   <si>
-    <t xml:space="preserve">Satisfactory (3 observations) – Word doc Section 1</t>
+    <t xml:space="preserve">Satisfactory (4 observations) – Word doc Section 1</t>
   </si>
   <si>
     <t xml:space="preserve">Sample result</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">1 Obtain evidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies (E01-E03), 2025 Q3 / 2026 Q1 certifications with AD extracts and Netwrix (E04-E05), management response (E06)</t>
+    <t xml:space="preserve">Policies (E01-E03), 2025 Q3 / 2026 Q1 certifications with AD extracts and Netwrix (E04-E05), management response (E07)</t>
   </si>
   <si>
     <t xml:space="preserve">Obtained; ServiceNow ticket not provided (O1)</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Removal by PAM/IAM within 30 business days of the close of the review</t>
   </si>
   <si>
-    <t xml:space="preserve">PASS - 2 business days</t>
+    <t xml:space="preserve">FAIL - removed in 2 business days (within SLA) but back in AD by 11/25/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Section 3 rows 7-8; Exhibit A3</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">6-7 Exceptions / escalation</t>
   </si>
   <si>
-    <t xml:space="preserve">No exceptions for this sample; observations recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A - observations O1-O3</t>
+    <t xml:space="preserve">Exception record, escalation (PAM Proc. sec. 4.2) and re-grant request for the returned access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAIL - none provided</t>
   </si>
   <si>
     <t xml:space="preserve">Section 3 rows 9-11</t>
@@ -182,13 +182,16 @@
     <t xml:space="preserve">Control mitigates inappropriate privileged network access for the sample</t>
   </si>
   <si>
+    <t xml:space="preserve">FAIL - access identified as inappropriate was back within 3 months</t>
+  </si>
+  <si>
     <t xml:space="preserve">Section 2 last paragraph; Conclusion</t>
   </si>
   <si>
     <t xml:space="preserve">Conclusion</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample MIA25142 PASSED all control attributes (A1-A6): review initiated by InfoSec, performed by the authorized line manager, inappropriate access revoked and removed by PAM/IAM within the 30-business-day SLA (SUS.IAMS.4.2.5.21). Three observations, no exceptions. Word doc: Section 3 Conclusion.</t>
+    <t xml:space="preserve">Sample MIA25142 FAILED attribute A6 (access stays removed): review initiated by InfoSec, performed by the authorized line manager and documented; access removed on 09/02/2025 within the 30-business-day SLA (SUS.IAMS.4.2.5.21) but back in both groups by 11/25/2025 without a request or escalation (SUS.IAMS.4.2.5.10; PAM Proc. 4.1.1 C4, sec. 4.2), and approved again in 2026 Q1 (A5 - E3). Word doc: Section 3 Conclusion</t>
   </si>
   <si>
     <t xml:space="preserve">Sample MIA25142 – attribute testing against the control description</t>
@@ -221,7 +224,7 @@
     <t xml:space="preserve">2025 Q3 review (launched 08/01/2025) for H2 2025 and 2026 Q1 review (launched 04/09/2026) for H1 2026; MIA25142 included in both</t>
   </si>
   <si>
-    <t xml:space="preserve">E04; E05; E07 tab 2_Step-by-Step 4.1</t>
+    <t xml:space="preserve">E04; E05; E06 tab 2_Step-by-Step 4.1</t>
   </si>
   <si>
     <t xml:space="preserve">Section 3, row 1</t>
@@ -344,6 +347,33 @@
     <t xml:space="preserve">Section 3, row 8; Exhibit A3</t>
   </si>
   <si>
+    <t xml:space="preserve">Access stayed removed - persistence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - member of both groups again in AD on 11/25/2025; no approved request, Netwrix "member added" event or escalation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E04 AD row 1639; E06 4_Item Detail rows 19, 57; E06 5_Exceptions row 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3, row 9; Exhibit A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 Q1 review of the re-added access (E3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved 04/30/2026 without an approved re-grant request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E05 rows 3260, 3265; E06 4_Item Detail rows 107, 130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3, row 10; Exhibit A4</t>
+  </si>
+  <si>
     <t xml:space="preserve">O1</t>
   </si>
   <si>
@@ -353,10 +383,10 @@
     <t xml:space="preserve">Not provided by management; removal evidenced by Netwrix</t>
   </si>
   <si>
-    <t xml:space="preserve">E07 tab 7_Evidence Status #12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section 3, row 9</t>
+    <t xml:space="preserve">E06 tab 7_Evidence Status #12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3, row 13</t>
   </si>
   <si>
     <t xml:space="preserve">PAM Proc. 4.1.1 C3</t>
@@ -365,16 +395,16 @@
     <t xml:space="preserve">O2</t>
   </si>
   <si>
-    <t xml:space="preserve">Access after removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member of both groups again in AD on 11/25/2025; approved by the line manager on 04/30/2026, 07/27/2026 and 08/17/2026. A new grant after a confirmed removal - assessed under SUS.IAMS.4.2.3.4 (provisioning), not this control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E04 (row 1639); E05 (rows 3260, 3265); E06 (SOX rows 98-100, CyberArk rows 431-433); E07 #5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section 3, row 10; Exhibits A1, A2, A4</t>
+    <t xml:space="preserve">2026 Q2 status (after the period)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still approved: SOX Manager 07/27/2026, CyberArk Manager 08/17/2026; AD enabled 10/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E07 / E06 blue tabs: SOX rows 98-100, CyberArk rows 431-433, Oct10_2026Users row 1621; E06 9_Sample Tab Review row 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3, row 11; Exhibits A1, A2, A4</t>
   </si>
   <si>
     <t xml:space="preserve">SUS.IAMS.4.2.3.4 (provisioning control)</t>
@@ -383,16 +413,16 @@
     <t xml:space="preserve">O3</t>
   </si>
   <si>
-    <t xml:space="preserve">Account status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAMS Termination Date 12/31/2024 but Identity Inactive FALSE and AD enabled (11/25/2025, 05/15/2026, 10/10/2026) - termination not evidenced; HR is the authoritative source (SUS.IAMS.4.2.1.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E04; E05 (row 1636); E06 Oct10_2026Users (row 1621); E07 #4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section 3, row 11; Exhibits A4, A5</t>
+    <t xml:space="preserve">Account status (E2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAMS Termination Date 12/31/2024, but Identity Inactive FALSE and not excluded as "Terminated in HR" by SanIAM - contract extension pending Fieldglass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E06 tab S13 rows 100-102 vs 192-198; E06 7_Evidence Status #13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3, row 12; Exhibits A3, A5</t>
   </si>
   <si>
     <t xml:space="preserve">SUS.IAMS.4.2.1.1; 4.2.4.3 if HR confirms</t>
@@ -449,19 +479,34 @@
     <t xml:space="preserve">Removal 09/02/2025 vs deadline 10/10/2025; SUS.IAMS.4.2.5.21 (p.22)</t>
   </si>
   <si>
-    <t xml:space="preserve">E07 Testing Walkthrough workbook</t>
+    <t xml:space="preserve">E04 BSI.IT.27.C7.02 Q3_2025.xlsx (AD extract); E06 walkthrough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD 11/25/2025 row 1639; 4_Item Detail rows 19, 57 (col V); 5_Exceptions row 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E05 BSI.IT.27.C7.02 Q1 2026 Cert.xlsx; E06 walkthrough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows 3260, 3265; 4_Item Detail rows 107, 130 (col U)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E06 Testing Walkthrough workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Tab 7_Evidence Status #12</t>
   </si>
   <si>
-    <t xml:space="preserve">E04 / E05 / E06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AD 11/25/2025 row 1639; Q1 2026 rows 3260, 3265; C7.Sample SOX rows 98-100, CyberArk rows 431-433; SAMPLE tab screenshots A14, A20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAMS Termination Date / Identity Inactive fields; AD 05/15/2026 row 1636; Oct10_2026Users row 1621</t>
+    <t xml:space="preserve">E07 C7.Sample.xlsx / E06 blue tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX Manager rows 98-100; CyberArk Manager rows 431-433; Oct10_2026Users row 1621; SAMPLE screenshots A14, A20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E06 tab S13 (SanIAM source)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIA25142 rows 100-102 (not excluded) vs rows 192-198 (excluded - Terminated in HR)</t>
   </si>
   <si>
     <t xml:space="preserve">Evidence index – BSI.IT.27.C7 (E01 – E09)</t>
@@ -584,6 +629,27 @@
     <t xml:space="preserve">E06</t>
   </si>
   <si>
+    <t xml:space="preserve">BSI.IT.27.C7.05 Testing Walkthrough - Combined with 2026 Q2 Sample.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing workpaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/2026 - IT RCSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_Attribute Matrix rows 5-6; 4_Item Detail rows 19, 57, 107, 130; 7_Evidence Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1-A6; O1-O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence references; closing note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E07</t>
+  </si>
+  <si>
     <t xml:space="preserve">C7.Sample.xlsx (management response)</t>
   </si>
   <si>
@@ -602,27 +668,6 @@
     <t xml:space="preserve">Exhibits A1, A2, A4, A5</t>
   </si>
   <si>
-    <t xml:space="preserve">E07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSI.IT.27.C7.05 Testing Walkthrough - Combined with 2026 Q2 Sample.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing workpaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/2026 - IT RCSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_Attribute Matrix rows 5-6; 4_Item Detail rows 19, 57, 107, 130; 7_Evidence Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1-A6; O1-O3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence references; closing note</t>
-  </si>
-  <si>
     <t xml:space="preserve">E08</t>
   </si>
   <si>
@@ -707,13 +752,31 @@
     <t xml:space="preserve">Sample Attribute Testing!A5:G12</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Sample of One – rows 9-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observations O1-O3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample Attribute Testing!A15:G17</t>
+    <t xml:space="preserve">3. Sample of One – rows 9-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A6 persistence and A5 (E3) – FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Attribute Testing!A13:G14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Sample of One – rows 11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Attribute Testing!A17:G19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Evidence Locator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every place MIA25142 appears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence Map; Evidence Index</t>
   </si>
   <si>
     <t xml:space="preserve">3. Conclusion</t>
@@ -737,7 +800,7 @@
     <t xml:space="preserve">2026 Q2 SOX Manager certification screenshot (rows 98-100)</t>
   </si>
   <si>
-    <t xml:space="preserve">Evidence Map (O2); Evidence Index E06</t>
+    <t xml:space="preserve">Evidence Map (O2); Evidence Index E07</t>
   </si>
   <si>
     <t xml:space="preserve">Exhibit A2</t>
@@ -761,7 +824,7 @@
     <t xml:space="preserve">Account and access status after the revocation</t>
   </si>
   <si>
-    <t xml:space="preserve">Evidence Map (O2, O3); Evidence Index E05, E06</t>
+    <t xml:space="preserve">Evidence Map (O2, O3); Evidence Index E05, E07</t>
   </si>
   <si>
     <t xml:space="preserve">Exhibit A5</t>
@@ -770,7 +833,7 @@
     <t xml:space="preserve">AD user export command screenshot</t>
   </si>
   <si>
-    <t xml:space="preserve">Evidence Map (O3); Evidence Index E06</t>
+    <t xml:space="preserve">Evidence Map (O3); Evidence Index E07</t>
   </si>
 </sst>
 </file>
@@ -842,7 +905,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -856,7 +919,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,7 +953,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -980,7 +1049,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -996,15 +1065,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1031,7 +1100,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -1062,7 +1131,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1330,20 +1399,20 @@
         <v>9</v>
       </c>
       <c r="E4" s="6" t="n">
-        <f aca="false">COUNTA('Sample Attribute Testing'!E5:E12)</f>
-        <v>8</v>
+        <f aca="false">COUNTA('Sample Attribute Testing'!E5:E14)</f>
+        <v>10</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIF('Sample Attribute Testing'!E5:E12,"PASS")</f>
+        <f aca="false">COUNTIF('Sample Attribute Testing'!E5:E14,"PASS")</f>
         <v>8</v>
       </c>
       <c r="G4" s="6" t="n">
         <f aca="false">E4-F4</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="7" t="str">
         <f aca="false">IF(G4=0,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1384,7 +1453,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTA('Sample Attribute Testing'!A15:A17)</f>
+        <f aca="false">COUNTA('Sample Attribute Testing'!A17:A19)</f>
         <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
@@ -1419,8 +1488,8 @@
         <v>21</v>
       </c>
       <c r="B9" s="9" t="str">
-        <f aca="false">IF(COUNTIF('Sample Attribute Testing'!E5:E12,"PASS")=COUNTA('Sample Attribute Testing'!E5:E12),"PASS – all attributes met","FAIL")</f>
-        <v>PASS – all attributes met</v>
+        <f aca="false">IF(COUNTIF('Sample Attribute Testing'!E5:E14,"PASS")=COUNTA('Sample Attribute Testing'!E5:E14),"PASS – all attributes met","FAIL")</f>
+        <v>FAIL</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1531,12 +1600,12 @@
         <v>43</v>
       </c>
       <c r="C18" s="6"/>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="6" t="s">
         <v>45</v>
       </c>
@@ -1549,12 +1618,12 @@
         <v>47</v>
       </c>
       <c r="C19" s="6"/>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="6" t="s">
         <v>49</v>
       </c>
@@ -1567,29 +1636,29 @@
         <v>51</v>
       </c>
       <c r="C20" s="6"/>
-      <c r="D20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="15" t="s">
+      <c r="A22" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+      <c r="B22" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1625,7 +1694,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1639,7 +1708,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1650,7 +1719,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1661,16 +1730,16 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>29</v>
@@ -1679,291 +1748,337 @@
         <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>117</v>
-      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="E17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="13" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="str">
-        <f aca="false">"Sample result: "&amp;IF(COUNTIF(E5:E12,"PASS")=COUNTA(E5:E12),"PASS","FAIL")&amp;" – "&amp;COUNTIF(E5:E12,"PASS")&amp;" of "&amp;COUNTA(E5:E12)&amp;" attribute checks passed; "&amp;COUNTA(A15:A17)&amp;" observations."</f>
-        <v>Sample result: PASS – 8 of 8 attribute checks passed; 3 observations.</v>
-      </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="F18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="str">
+        <f aca="false">"Sample result: "&amp;IF(COUNTIF(E5:E14,"PASS")=COUNTA(E5:E14),"PASS","FAIL")&amp;" – "&amp;COUNTIF(E5:E14,"PASS")&amp;" of "&amp;COUNTA(E5:E14)&amp;" attribute checks passed; "&amp;COUNTA(A17:A19)&amp;" observations."</f>
+        <v>Sample result: FAIL – 8 of 10 attribute checks passed; 3 observations.</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A21:G21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1980,7 +2095,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1992,7 +2107,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2001,7 +2116,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2010,16 +2125,16 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>30</v>
@@ -2027,189 +2142,223 @@
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="C14" s="6" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>122</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2246,7 +2395,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2257,7 +2406,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2268,22 +2417,22 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>30</v>
@@ -2291,209 +2440,209 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>197</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2516,7 +2665,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -2526,31 +2675,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2558,131 +2707,153 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>248</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx
+++ b/BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">BSI.IT.27.C7 – Network Device Admin Account Review – Sample of One Workpaper (MIA25142)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supports the Word document "BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx". Each row gives the matching section / exhibit of that document.</t>
+    <t xml:space="preserve">Supports the Word document "BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx (folder BSI.IT.27.C7)". Each row gives the matching section / exhibit of that document.</t>
   </si>
   <si>
     <t xml:space="preserve">KPI</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Word document</t>
   </si>
   <si>
-    <t xml:space="preserve">BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx</t>
+    <t xml:space="preserve">BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx (folder BSI.IT.27.C7)</t>
   </si>
   <si>
     <t xml:space="preserve">Walkthrough</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">E01</t>
   </si>
   <si>
-    <t xml:space="preserve">CUSO Identity and Access Management Standard v11.0 (BSIIT21.PDF)</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E01_IAM Standard v11.0 (BSIIT21).pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Policy</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">E02</t>
   </si>
   <si>
-    <t xml:space="preserve">PAM Recertification Procedure (BSI) 04.22.26.pdf (v2.0)</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E02_PAM Recertification Procedure (BSI) 04.22.26.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">04/22/2026 - BSI CISO</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">E03</t>
   </si>
   <si>
-    <t xml:space="preserve">BSI.IT.27.C7.03 PAM Definition of Privilege.pdf (v10.0)</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E03_PAM Definition of Privilege.pdf (not in package)</t>
   </si>
   <si>
     <t xml:space="preserve">03/11/2025</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">E04</t>
   </si>
   <si>
-    <t xml:space="preserve">BSI.IT.27.C7.02 Q3_2025.xlsx</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E04_Q3_2025.xlsx (not in package)</t>
   </si>
   <si>
     <t xml:space="preserve">SailPoint export, AD extract, Netwrix log</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">E05</t>
   </si>
   <si>
-    <t xml:space="preserve">BSI.IT.27.C7.02 Q1 2026 Cert.xlsx</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E05_Q1 2026 Cert.xlsx (not in package)</t>
   </si>
   <si>
     <t xml:space="preserve">SailPoint export, AD extract</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">E06</t>
   </si>
   <si>
-    <t xml:space="preserve">BSI.IT.27.C7.05 Testing Walkthrough - Combined with 2026 Q2 Sample.xlsx</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E06_Testing Walkthrough - Combined with 2026 Q2 Sample.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Testing workpaper</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">E07</t>
   </si>
   <si>
-    <t xml:space="preserve">C7.Sample.xlsx (management response)</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E07_C7.Sample.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">SailPoint exports, AD user export, screenshots</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">E08</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample step taken.docx</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E08_Sample step taken.docx</t>
   </si>
   <si>
     <t xml:space="preserve">Request</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">E09</t>
   </si>
   <si>
-    <t xml:space="preserve">BSI.IT.27.C7_Sample_of_1_MIA25142_Workpaper.xlsx (this workbook)</t>
+    <t xml:space="preserve">BSI.IT.27.C7_E09_Sample of 1 MIA25142 Workpaper.xlsx (this workbook)</t>
   </si>
   <si>
     <t xml:space="preserve">Sample result, attribute testing, evidence map and index for MIA25142</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">Summary box; Section 3 (evidence column, conclusion); Evidence references E09; Exhibits A1-A5</t>
   </si>
   <si>
-    <t xml:space="preserve">Cross-reference: BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx → this workbook</t>
+    <t xml:space="preserve">Cross-reference: BSI.IT.27.C7_Design_WT_Sample_of_1_MIA25142.docx (folder BSI.IT.27.C7) → this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Word document section / exhibit</t>
